--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6188-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6188-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2378ADAF-008C-4040-857D-F99890B30BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83107670-D5F0-41A2-997B-3CCF33DDCEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0F6BC9CF-83B7-48CD-A1B1-5484A8C4792B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{104BFAB0-FEC4-442D-8BB4-9CFAF228ED6A}"/>
   </bookViews>
   <sheets>
     <sheet name="6188-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1489,25 +1489,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E45ECB-55D0-414D-B1AC-BA8A94C955F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455067FA-8450-4AC2-8240-DCB05891A7DB}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1661,7 +1661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2026</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
       <c r="B6" s="43"/>
       <c r="C6" s="45"/>
@@ -1741,7 +1741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>2025</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="52">
         <v>2024</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="50">
         <v>2023</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="52">
         <v>2022</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>2021</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="52">
         <v>2020</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <v>2019</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>2018</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="50">
         <v>2017</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="52">
         <v>2016</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>2015</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="52">
         <v>2014</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>2013</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>2012</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>2011</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="52">
         <v>2010</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>2009</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="52">
         <v>2008</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>2007</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="52">
         <v>2006</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>2005</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="52">
         <v>2004</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>2003</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="52">
         <v>2002</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="50">
         <v>2001</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="52">
         <v>2000</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="50" t="s">
         <v>33</v>
       </c>
